--- a/college-posters/data/字段表_最后一批.xlsx
+++ b/college-posters/data/字段表_最后一批.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -485,12 +485,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>天津医科大学校训原文未核到，竖排改放运营寄语“仁心精术”，印章写“寄语”</t>
+          <t>求真至善；已替换原运营寄语</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>待核（校训原文）</t>
+          <t>待核（单一来源）</t>
         </is>
       </c>
     </row>
@@ -524,61 +524,61 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>三甲医院、医药企业、医学科研</t>
+          <t>气象台路校区：天津主校区；广东路校区：新校区；附属医院：天津医科大学总医院等</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>天津医科大学</t>
+          <t>中国传媒大学</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>气象台路校区：天津主校区；广东路校区：新校区；附属医院：天津医科大学总医院等</t>
+          <t>播音与主持艺术、新闻学、广播电视编导、戏剧影视文学、数字媒体技术、网络与新媒体</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>天津医科大学</t>
+          <t>中国传媒大学</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>医学类专业：物理 + 化学；其他专业：以当年招生章程为准</t>
+          <t>定福庄校区：朝阳主校区；梧桐大道：校园标志景观；传媒博物馆：广播电视历史展馆</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
@@ -590,46 +590,46 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>播音与主持艺术、新闻学、广播电视编导、戏剧影视文学、数字媒体技术、网络与新媒体</t>
+          <t>艺术类专业需参加专业考试；具体选科以当年招生章程为准</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>中国传媒大学</t>
+          <t>北京体育大学</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>广播电视与新媒体、影视与文化产业、互联网与广告</t>
+          <t>体育教育、运动训练、运动人体科学、运动康复、体育经济与管理、新闻学</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>中国传媒大学</t>
+          <t>北京体育大学</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>定福庄校区：朝阳主校区；梧桐大道：校园标志景观；传媒博物馆：广播电视历史展馆</t>
+          <t>主校区：圆明园东路；田径场：校园中心运动场；体育馆：综合训练场馆</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -651,29 +651,29 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>中国传媒大学</t>
+          <t>中央音乐学院</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校训</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>艺术类专业需参加专业考试；具体选科以当年招生章程为准</t>
+          <t>勤奋 求实 团结 进取；已替换原运营寄语</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核（单一来源）</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>北京体育大学</t>
+          <t>中央音乐学院</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>体育教育、运动训练、运动人体科学、运动康复、体育经济与管理、新闻学</t>
+          <t>作曲与作曲技术理论、音乐表演、音乐学、音乐教育、录音艺术、艺术管理</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -695,139 +695,139 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>北京体育大学</t>
+          <t>中央音乐学院</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>体育教育与训练、运动康复与健康、体育产业与媒体</t>
+          <t>鲍家街校区：西城主校区；音乐厅：校内演出场所；雄安校区：新建校区</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>北京体育大学</t>
+          <t>国防科技大学</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>主校区：圆明园东路；田径场：校园中心运动场；体育馆：综合训练场馆</t>
+          <t>计算机科学与技术、电子信息工程、航空航天工程、软件工程、光电信息科学与工程、管理科学与工程</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>北京体育大学</t>
+          <t>国防科技大学</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>体育类专业：需参加体育专业考试；其他专业：以当年招生章程为准</t>
+          <t>主校区：长沙开福区；哈军工旧址：前身所在地哈尔滨；图书馆：主校区标志建筑</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>中央音乐学院</t>
+          <t>国防科技大学</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>校训</t>
+          <t>选科要求</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>中央音乐学院校训原文未核到，竖排改放运营寄语“乐以载道”，印章写“寄语”</t>
+          <t>军队院校选科、政治考核、军检以当年军队院校招生规定为准</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>待核（校训原文）</t>
+          <t>待核2027年军队院校招生规定</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>中央音乐学院</t>
+          <t>海军军医大学</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>校训</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>作曲与作曲技术理论、音乐表演、音乐学、音乐教育、录音艺术、艺术管理</t>
+          <t>海军军医大学校训原文未核到，竖排改放运营寄语“军医报国”，印章写“寄语”</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核（校训原文）</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>中央音乐学院</t>
+          <t>海军军医大学</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>专业乐团与演出、音乐教育、文化与传媒</t>
+          <t>临床医学、基础医学、药学、护理学、预防医学、麻醉学</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>中央音乐学院</t>
+          <t>海军军医大学</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>鲍家街校区：西城主校区；音乐厅：校内演出场所；雄安校区：新建校区</t>
+          <t>主校区：上海杨浦；长海医院：附属医院；长征医院：附属医院</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -849,7 +849,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>中央音乐学院</t>
+          <t>海军军医大学</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -859,63 +859,63 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>艺术类专业：需参加专业考试（校考/统考）；选科要求：以当年招生章程为准</t>
+          <t>军队院校选科、政治考核、军检以当年军队院校招生规定为准</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核2027年军队院校招生规定</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>国防科技大学</t>
+          <t>空军军医大学</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>王牌专业</t>
+          <t>校训</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>计算机科学与技术、电子信息工程、航空航天工程、软件工程、光电信息科学与工程、管理科学与工程</t>
+          <t>空军军医大学校训原文未核到，竖排改放运营寄语“仁医强军”，印章写“寄语”</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>待核当年招生专业目录</t>
+          <t>待核（校训原文）</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>国防科技大学</t>
+          <t>空军军医大学</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>部队技术与指挥岗位、国防科研院所、军队院校</t>
+          <t>临床医学、口腔医学、基础医学、药学、护理学、预防医学</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>国防科技大学</t>
+          <t>空军军医大学</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>主校区：长沙开福区；哈军工旧址：前身所在地哈尔滨；图书馆：主校区标志建筑</t>
+          <t>主校区：西安长乐西路；西京医院：附属医院；唐都医院：附属医院</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -937,7 +937,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>国防科技大学</t>
+          <t>空军军医大学</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -951,226 +951,6 @@
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年军队院校招生规定</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>海军军医大学</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>校训</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>海军军医大学校训原文未核到，竖排改放运营寄语“军医报国”，印章写“寄语”</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>待核（校训原文）</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>海军军医大学</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>临床医学、基础医学、药学、护理学、预防医学、麻醉学</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>海军军医大学</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>部队医院、军队医学科研、卫勤保障岗位</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>海军军医大学</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>主校区：上海杨浦；长海医院：附属医院；长征医院：附属医院</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>海军军医大学</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>军队院校选科、政治考核、军检以当年军队院校招生规定为准</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年军队院校招生规定</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>空军军医大学</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>校训</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>空军军医大学校训原文未核到，竖排改放运营寄语“仁医强军”，印章写“寄语”</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>待核（校训原文）</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>空军军医大学</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>临床医学、口腔医学、基础医学、药学、护理学、预防医学</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>空军军医大学</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>部队医院、军队医学科研、卫勤保障岗位</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>空军军医大学</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>主校区：西安长乐西路；西京医院：附属医院；唐都医院：附属医院</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>空军军医大学</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>军队院校选科、政治考核、军检以当年军队院校招生规定为准</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>待核2027年军队院校招生规定</t>
         </is>
@@ -1339,22 +1119,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>天津医科大学校训原文未核到，竖排改放运营寄语“仁心精术”，印章写“寄语”</t>
+          <t>求真至善；已替换原运营寄语</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>仁心 精术</t>
+          <t>求真 至善</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>买购网（单一来源）</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>待核（校训原文）</t>
+          <t>待核（单一来源）</t>
         </is>
       </c>
     </row>
@@ -1736,9 +1516,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -1861,12 +1641,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -2494,9 +2274,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -2619,7 +2399,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -3252,9 +3032,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -3377,12 +3157,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -3613,22 +3393,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>中央音乐学院校训原文未核到，竖排改放运营寄语“乐以载道”，印章写“寄语”</t>
+          <t>勤奋 求实 团结 进取；已替换原运营寄语</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>乐以 载道</t>
+          <t>勤奋求实 团结进取</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>买购网（单一来源）</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>待核（校训原文）</t>
+          <t>待核（单一来源）</t>
         </is>
       </c>
     </row>
@@ -4010,9 +3790,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -4135,12 +3915,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -4768,9 +4548,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -4893,7 +4673,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -5526,9 +5306,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5431,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -6284,9 +6064,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -6409,7 +6189,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
